--- a/data/trans_dic/P13A_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,5</t>
+          <t>0,6; 2,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,11</t>
+          <t>2,49; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,38</t>
+          <t>1,84; 3,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,23</t>
+          <t>0,56; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,96</t>
+          <t>3,63; 6,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,56</t>
+          <t>1,81; 3,6</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,19</t>
+          <t>0,54; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,84</t>
+          <t>1,63; 4,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,22</t>
+          <t>1,5; 3,27</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,22</t>
+          <t>0,31; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,93</t>
+          <t>2,98; 5,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,43</t>
+          <t>1,85; 3,53</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,5</t>
+          <t>0,73; 1,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,75</t>
+          <t>3,18; 4,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,98</t>
+          <t>2,16; 2,98</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4178; 15793</t>
+          <t>3807; 15518</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16776; 34474</t>
+          <t>16813; 35433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23647; 44226</t>
+          <t>24027; 44374</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5837; 26581</t>
+          <t>6625; 26490</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33923; 57000</t>
+          <t>34743; 58893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38232; 76506</t>
+          <t>38944; 77263</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3550; 15419</t>
+          <t>3830; 16724</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15368; 45105</t>
+          <t>15142; 43660</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24559; 52589</t>
+          <t>24494; 53487</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2372; 11279</t>
+          <t>2817; 12040</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31164; 64415</t>
+          <t>32345; 63720</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37083; 68982</t>
+          <t>37218; 70901</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25102; 51787</t>
+          <t>25203; 51393</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118711; 173404</t>
+          <t>116137; 172756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>152673; 211370</t>
+          <t>153163; 211769</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13A_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,45</t>
+          <t>0,57; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,26</t>
+          <t>2,48; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,4</t>
+          <t>1,71; 3,4</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,23</t>
+          <t>0,85; 2,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,15</t>
+          <t>3,57; 5,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,6</t>
+          <t>2,41; 3,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,38</t>
+          <t>0,67; 2,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,69</t>
+          <t>3,24; 5,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,27</t>
+          <t>2,29; 3,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,3</t>
+          <t>0,29; 1,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,87</t>
+          <t>3,11; 5,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,53</t>
+          <t>1,84; 3,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,49</t>
+          <t>0,83; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,74</t>
+          <t>3,65; 4,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,98</t>
+          <t>2,32; 3,07</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>33860</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3807; 15518</t>
+          <t>3948; 15740</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16813; 35433</t>
+          <t>18119; 37356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24027; 44374</t>
+          <t>24295; 48233</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44141</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58909</t>
+          <t>64003</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6625; 26490</t>
+          <t>8903; 26815</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34743; 58893</t>
+          <t>38220; 63521</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38944; 77263</t>
+          <t>50957; 82466</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>46360</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3830; 16724</t>
+          <t>5368; 19159</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15142; 43660</t>
+          <t>26171; 46134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24494; 53487</t>
+          <t>36881; 59365</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>50766</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2817; 12040</t>
+          <t>2897; 12589</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32345; 63720</t>
+          <t>34416; 59495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37218; 70901</t>
+          <t>38615; 65660</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25203; 51393</t>
+          <t>29269; 55553</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>116137; 172756</t>
+          <t>135676; 179204</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153163; 211769</t>
+          <t>168200; 222488</t>
         </is>
       </c>
     </row>
